--- a/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
+++ b/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,7 +483,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>l-85009</t>
+          <t>I-9265</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,22 +508,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-4.576882</t>
+          <t>-4.5899054</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-81.264847</t>
+          <t>-81.2267974</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -535,7 +535,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>l-85018</t>
+          <t>I-84964</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -560,25 +560,1169 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-4.5770031</t>
+          <t>-4.5750172</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-81.2646167</t>
+          <t>-81.2699834</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>I-199685</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-4.580042</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>-81.2716306</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Avenida Mariscal Castilla / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>I-85009</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-4.576882</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>-81.264847</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>I-412492</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-4.5936624</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>-81.2605962</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Antonio Jose de Sucre / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>I-412490</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-4.5935574</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>-81.2617073</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Antonio Jose de Sucre / Francisco Bolognesi / Pasaje Bolívar</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>I-412486</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-4.5944036</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>-81.2627963</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>I-412477</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-4.5920756</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>-81.2623592</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>I-412476</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-4.5899547</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>-81.2630002</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>I-412473</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-4.5917139</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>-81.2563081</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Avenida Z / Calle 4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>I-412471</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-4.5931119</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>-81.2664062</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>I-412470</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-4.5971667</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>-81.2683619</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>I-412469</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-4.5954505</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>-81.268366</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>I-412467</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-4.5967804</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>-81.2719318</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>I-412465</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-4.5957377</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>-81.2719816</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>I-412523</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-4.5940894</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>-81.2543728</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>I-412531</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-4.594179</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>-81.2566219</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>I-199581</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>200705</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>LOS ORGANOS</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-4.1811216</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-81.1254179</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>I-412439</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-4.5966225</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-81.2501233</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>I-412453</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-4.5935292</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-81.2516469</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>I-412449</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-4.5941209</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-81.2509118</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>I-412443</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>-4.5949877</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-81.2512441</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>I-412436</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>-4.5928489</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-81.2525127</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>I-412433</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-4.5962215</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-81.2543029</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
         <is>
           <t>200701</t>
         </is>

--- a/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
+++ b/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1728,6 +1728,318 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>I-9266</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>-4.5649311</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-81.2183989</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>I-412409</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-4.5891018</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-81.2598459</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>I-412425</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-4.6005644</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-81.2587416</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>I-412424</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-4.600615</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-81.2583834</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>I-412423</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>-4.5919955</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-81.2573772</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Avenida Z / Calle 2</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>I-18456</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>200706</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>MANCORA</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-4.1145653</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-81.0786769</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
+++ b/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2040,6 +2040,58 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>I-18455</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>200705</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LOS ORGANOS</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-4.1318864</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-81.101467</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
+++ b/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
@@ -425,35 +425,35 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
+          <t>ubigeo_gestor</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>DEPARTAMENTO</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>PROVINCIA</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>DISTRITO</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ID_INT</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>UBIGEO</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>DEPARTAMENTO</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>PROVINCIA</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>DISTRITO</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
           <t>LATITUD</t>
@@ -472,40 +472,35 @@
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>ubigeo_gestor</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>I-9265</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
           <t>-4.5899054</t>
@@ -524,40 +519,35 @@
       <c r="I2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>I-84964</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>-4.5750172</t>
@@ -576,40 +566,35 @@
       <c r="I3" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>I-199685</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F4" t="inlineStr">
         <is>
           <t>-4.580042</t>
@@ -628,40 +613,35 @@
       <c r="I4" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>I-85009</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
           <t>-4.576882</t>
@@ -680,40 +660,35 @@
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>I-412492</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F6" t="inlineStr">
         <is>
           <t>-4.5936624</t>
@@ -732,40 +707,35 @@
       <c r="I6" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>I-412490</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>-4.5935574</t>
@@ -784,40 +754,35 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>I-412486</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F8" t="inlineStr">
         <is>
           <t>-4.5944036</t>
@@ -836,40 +801,35 @@
       <c r="I8" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>I-412477</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F9" t="inlineStr">
         <is>
           <t>-4.5920756</t>
@@ -888,40 +848,35 @@
       <c r="I9" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>I-412476</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F10" t="inlineStr">
         <is>
           <t>-4.5899547</t>
@@ -940,40 +895,35 @@
       <c r="I10" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>I-412473</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F11" t="inlineStr">
         <is>
           <t>-4.5917139</t>
@@ -992,40 +942,35 @@
       <c r="I11" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>I-412471</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F12" t="inlineStr">
         <is>
           <t>-4.5931119</t>
@@ -1044,40 +989,35 @@
       <c r="I12" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>I-412470</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F13" t="inlineStr">
         <is>
           <t>-4.5971667</t>
@@ -1096,40 +1036,35 @@
       <c r="I13" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>I-412469</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F14" t="inlineStr">
         <is>
           <t>-4.5954505</t>
@@ -1148,40 +1083,35 @@
       <c r="I14" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>I-412467</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F15" t="inlineStr">
         <is>
           <t>-4.5967804</t>
@@ -1200,40 +1130,35 @@
       <c r="I15" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>I-412465</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F16" t="inlineStr">
         <is>
           <t>-4.5957377</t>
@@ -1252,40 +1177,35 @@
       <c r="I16" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>I-412523</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F17" t="inlineStr">
         <is>
           <t>-4.5940894</t>
@@ -1304,40 +1224,35 @@
       <c r="I17" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>I-412531</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F18" t="inlineStr">
         <is>
           <t>-4.594179</t>
@@ -1356,40 +1271,35 @@
       <c r="I18" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>I-199581</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>200705</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>LOS ORGANOS</t>
-        </is>
-      </c>
       <c r="F19" t="inlineStr">
         <is>
           <t>-4.1811216</t>
@@ -1408,40 +1318,35 @@
       <c r="I19" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>I-412439</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F20" t="inlineStr">
         <is>
           <t>-4.5966225</t>
@@ -1460,40 +1365,35 @@
       <c r="I20" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>I-412453</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-4.5935292</t>
@@ -1512,40 +1412,35 @@
       <c r="I21" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>I-412449</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F22" t="inlineStr">
         <is>
           <t>-4.5941209</t>
@@ -1564,40 +1459,35 @@
       <c r="I22" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>I-412443</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F23" t="inlineStr">
         <is>
           <t>-4.5949877</t>
@@ -1616,40 +1506,35 @@
       <c r="I23" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>I-412436</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F24" t="inlineStr">
         <is>
           <t>-4.5928489</t>
@@ -1668,40 +1553,35 @@
       <c r="I24" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>I-412433</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F25" t="inlineStr">
         <is>
           <t>-4.5962215</t>
@@ -1720,40 +1600,35 @@
       <c r="I25" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>I-9266</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F26" t="inlineStr">
         <is>
           <t>-4.5649311</t>
@@ -1772,40 +1647,35 @@
       <c r="I26" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>I-412409</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F27" t="inlineStr">
         <is>
           <t>-4.5891018</t>
@@ -1824,40 +1694,35 @@
       <c r="I27" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>I-412425</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F28" t="inlineStr">
         <is>
           <t>-4.6005644</t>
@@ -1876,40 +1741,35 @@
       <c r="I28" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>I-412424</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F29" t="inlineStr">
         <is>
           <t>-4.600615</t>
@@ -1928,40 +1788,35 @@
       <c r="I29" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>I-412423</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>200701</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>PARIÑAS</t>
-        </is>
-      </c>
       <c r="F30" t="inlineStr">
         <is>
           <t>-4.5919955</t>
@@ -1980,40 +1835,35 @@
       <c r="I30" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>I-18456</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>200706</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>MANCORA</t>
-        </is>
-      </c>
       <c r="F31" t="inlineStr">
         <is>
           <t>-4.1145653</t>
@@ -2032,40 +1882,35 @@
       <c r="I31" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>I-18455</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>200705</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>PIURA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>TALARA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>LOS ORGANOS</t>
-        </is>
-      </c>
       <c r="F32" t="inlineStr">
         <is>
           <t>-4.1318864</t>
@@ -2084,11 +1929,6 @@
       <c r="I32" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>200701</t>
         </is>
       </c>
     </row>

--- a/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
+++ b/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ID_INT</t>
+          <t>Codigo</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">

--- a/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
+++ b/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,47 +417,47 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>ubigeo_gestor</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>DEPARTAMENTO</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>PROVINCIA</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>DISTRITO</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Codigo</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>LATITUD</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>LONGITUD</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Vias</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Siniestro_fatal</t>
         </is>

--- a/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
+++ b/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1920,6 +1920,523 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>I-85004</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>-4.5732755</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-81.2678659</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Av Yale con Av Angamos</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>I-85085</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>-4.5742271</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-81.2668009</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Av Fraser con Av Tarapacá</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>I-85021</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>-4.5733721</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-81.2747572</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>I-411147</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>-4.5747712</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-81.2726367</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>I-411330</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>-4.5803295</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-81.2687391</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Av. Mariscal Castilla con Av Martires Petroleros</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>I-411507</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-4.5800218</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-81.2723111</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Av Ramon Castilla con calle s/n</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>I-411347</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-4.5802351</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-81.2676767</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Calle s / n / Calle s / n</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>I-411334</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>-4.5791465</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-81.2684768</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Av Martires Petroleros con calle s/n</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>I-84959</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>-4.5749543</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-81.2663334</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Av Aviacion con Av Arica</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>I-490959</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-4.5751863</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-81.2656825</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Av Aviacion con Jr. Ayacucho</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>200701</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>PIURA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>TALARA</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>PARIÑAS</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>I-84985</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-4.5752343</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-81.2671585</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Av Ejercito con Jr. Tarapaca</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
+++ b/Intersecciones/excels/PIURA-TALARA-PARIÑAS.xlsx
@@ -486,17 +486,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>I-9265</t>
+          <t>I-9266</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-4.5899054</t>
+          <t>-4.5649311</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-81.2267974</t>
+          <t>-81.2183989</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -533,17 +533,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>I-84964</t>
+          <t>I-9265</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-4.5750172</t>
+          <t>-4.5899054</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-81.2699834</t>
+          <t>-81.2267974</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -580,22 +580,22 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>I-199685</t>
+          <t>I-85085</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>-4.580042</t>
+          <t>-4.5742271</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-81.2716306</t>
+          <t>-81.2668009</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Avenida Mariscal Castilla / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -627,27 +627,27 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>I-85009</t>
+          <t>I-85021</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>-4.576882</t>
+          <t>-4.5733721</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-81.264847</t>
+          <t>-81.2747572</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -674,27 +674,27 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>I-412492</t>
+          <t>I-85009</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>-4.5936624</t>
+          <t>-4.576882</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-81.2605962</t>
+          <t>-81.264847</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Antonio Jose de Sucre / Calle s / n</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>I-412490</t>
+          <t>I-85004</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>-4.5935574</t>
+          <t>-4.5732755</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-81.2617073</t>
+          <t>-81.2678659</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Antonio Jose de Sucre / Francisco Bolognesi / Pasaje Bolívar</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -768,17 +768,17 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>I-412486</t>
+          <t>I-84985</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-4.5944036</t>
+          <t>-4.5752343</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>-81.2627963</t>
+          <t>-81.2671585</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -815,17 +815,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>I-412477</t>
+          <t>I-84964</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-4.5920756</t>
+          <t>-4.5750172</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-81.2623592</t>
+          <t>-81.2699834</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -862,17 +862,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>I-412476</t>
+          <t>I-84959</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-4.5899547</t>
+          <t>-4.5749543</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-81.2630002</t>
+          <t>-81.2663334</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -909,22 +909,22 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>I-412473</t>
+          <t>I-490959</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-4.5917139</t>
+          <t>-4.5751863</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-81.2563081</t>
+          <t>-81.2656825</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Avenida Z / Calle 4</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -956,17 +956,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>I-412471</t>
+          <t>I-412531</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>-4.5931119</t>
+          <t>-4.594179</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>-81.2664062</t>
+          <t>-81.2566219</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1003,17 +1003,17 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>I-412470</t>
+          <t>I-412523</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>-4.5971667</t>
+          <t>-4.5940894</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>-81.2683619</t>
+          <t>-81.2543728</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1050,22 +1050,22 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>I-412469</t>
+          <t>I-412492</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>-4.5954505</t>
+          <t>-4.5936624</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>-81.268366</t>
+          <t>-81.2605962</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Antonio Jose de Sucre / Calle s / n</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1097,22 +1097,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>I-412467</t>
+          <t>I-412490</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>-4.5967804</t>
+          <t>-4.5935574</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>-81.2719318</t>
+          <t>-81.2617073</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Antonio Jose de Sucre / Francisco Bolognesi / Pasaje Bolívar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1144,17 +1144,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>I-412465</t>
+          <t>I-412486</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-4.5957377</t>
+          <t>-4.5944036</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-81.2719816</t>
+          <t>-81.2627963</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1191,17 +1191,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>I-412523</t>
+          <t>I-412477</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>-4.5940894</t>
+          <t>-4.5920756</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>-81.2543728</t>
+          <t>-81.2623592</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1238,17 +1238,17 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>I-412531</t>
+          <t>I-412476</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>-4.594179</t>
+          <t>-4.5899547</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>-81.2566219</t>
+          <t>-81.2630002</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1285,22 +1285,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>I-199581</t>
+          <t>I-412473</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>-4.1811216</t>
+          <t>-4.5917139</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>-81.1254179</t>
+          <t>-81.2563081</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>Avenida Z / Calle 4</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1332,17 +1332,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>I-412439</t>
+          <t>I-412471</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-4.5966225</t>
+          <t>-4.5931119</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-81.2501233</t>
+          <t>-81.2664062</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1379,17 +1379,17 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>I-412453</t>
+          <t>I-412470</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>-4.5935292</t>
+          <t>-4.5971667</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>-81.2516469</t>
+          <t>-81.2683619</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1426,17 +1426,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>I-412449</t>
+          <t>I-412469</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>-4.5941209</t>
+          <t>-4.5954505</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>-81.2509118</t>
+          <t>-81.268366</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1473,17 +1473,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>I-412443</t>
+          <t>I-412467</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>-4.5949877</t>
+          <t>-4.5967804</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>-81.2512441</t>
+          <t>-81.2719318</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1520,17 +1520,17 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>I-412436</t>
+          <t>I-412465</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>-4.5928489</t>
+          <t>-4.5957377</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>-81.2525127</t>
+          <t>-81.2719816</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1567,17 +1567,17 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>I-412433</t>
+          <t>I-412453</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>-4.5962215</t>
+          <t>-4.5935292</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>-81.2543029</t>
+          <t>-81.2516469</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1614,17 +1614,17 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>I-9266</t>
+          <t>I-412449</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>-4.5649311</t>
+          <t>-4.5941209</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>-81.2183989</t>
+          <t>-81.2509118</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1661,17 +1661,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>I-412409</t>
+          <t>I-412443</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-4.5891018</t>
+          <t>-4.5949877</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-81.2598459</t>
+          <t>-81.2512441</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1708,17 +1708,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>I-412425</t>
+          <t>I-412439</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>-4.6005644</t>
+          <t>-4.5966225</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>-81.2587416</t>
+          <t>-81.2501233</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1755,17 +1755,17 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>I-412424</t>
+          <t>I-412436</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-4.600615</t>
+          <t>-4.5928489</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-81.2583834</t>
+          <t>-81.2525127</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1802,22 +1802,22 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>I-412423</t>
+          <t>I-412433</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>-4.5919955</t>
+          <t>-4.5962215</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>-81.2573772</t>
+          <t>-81.2543029</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Avenida Z / Calle 2</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1849,17 +1849,17 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>I-18456</t>
+          <t>I-412425</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>-4.1145653</t>
+          <t>-4.6005644</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>-81.0786769</t>
+          <t>-81.2587416</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1896,17 +1896,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>I-18455</t>
+          <t>I-412424</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>-4.1318864</t>
+          <t>-4.600615</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>-81.101467</t>
+          <t>-81.2583834</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1943,22 +1943,22 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>I-85004</t>
+          <t>I-412423</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>-4.5732755</t>
+          <t>-4.5919955</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>-81.2678659</t>
+          <t>-81.2573772</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Av Yale con Av Angamos</t>
+          <t>Avenida Z / Calle 2</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1990,22 +1990,22 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>I-85085</t>
+          <t>I-412409</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>-4.5742271</t>
+          <t>-4.5891018</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>-81.2668009</t>
+          <t>-81.2598459</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Av Fraser con Av Tarapacá</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>I-85021</t>
+          <t>I-411507</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>-4.5733721</t>
+          <t>-4.5800218</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>-81.2747572</t>
+          <t>-81.2723111</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>I-411147</t>
+          <t>I-411347</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>-4.5747712</t>
+          <t>-4.5802351</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>-81.2726367</t>
+          <t>-81.2676767</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2131,22 +2131,22 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>I-411330</t>
+          <t>I-411334</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>-4.5803295</t>
+          <t>-4.5791465</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>-81.2687391</t>
+          <t>-81.2684768</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Av. Mariscal Castilla con Av Martires Petroleros</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2178,22 +2178,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>I-411507</t>
+          <t>I-411330</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>-4.5800218</t>
+          <t>-4.5803295</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>-81.2723111</t>
+          <t>-81.2687391</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Av Ramon Castilla con calle s/n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2225,22 +2225,22 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>I-411347</t>
+          <t>I-411147</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>-4.5802351</t>
+          <t>-4.5747712</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>-81.2676767</t>
+          <t>-81.2726367</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Calle s / n / Calle s / n</t>
+          <t>calle sn / calle s/n</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>I-411334</t>
+          <t>I-199685</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-4.5791465</t>
+          <t>-4.580042</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-81.2684768</t>
+          <t>-81.2716306</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Av Martires Petroleros con calle s/n</t>
+          <t>Avenida Mariscal Castilla / Calle s / n</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2319,22 +2319,22 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>I-84959</t>
+          <t>I-199581</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>-4.5749543</t>
+          <t>-4.1811216</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>-81.2663334</t>
+          <t>-81.1254179</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Av Aviacion con Av Arica</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2366,22 +2366,22 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>I-490959</t>
+          <t>I-18456</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>-4.5751863</t>
+          <t>-4.1145653</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>-81.2656825</t>
+          <t>-81.0786769</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Av Aviacion con Jr. Ayacucho</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2413,22 +2413,22 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>I-84985</t>
+          <t>I-18455</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-4.5752343</t>
+          <t>-4.1318864</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-81.2671585</t>
+          <t>-81.101467</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Av Ejercito con Jr. Tarapaca</t>
+          <t>Calle s / n / Calle s / n</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
